--- a/光伏配储项目/电价数据/2026/青溪厂.xlsx
+++ b/光伏配储项目/电价数据/2026/青溪厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42206</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7301799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48601</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.42602</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.22819</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.10224</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.10125</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.46596</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.67536</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.96396</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.29355</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.64559</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.87097</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.18879</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.32166</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17877</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.01936</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.25106</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.25866</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6791200000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.74164</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.0402</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9759099999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87471</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.78603</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7446499999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50656</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43357</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69835</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8803799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9284600000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52611</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.46694</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.49696</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.51367</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.40653</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.39639</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.53226</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.54869</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47872</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18014</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.43972</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5442899999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.21276</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.01722</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5962799999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74866</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.77679</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15587</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.21891</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.12679</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.7944099999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.18639</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.05017</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.05455</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.82784</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.0769</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63564</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.97366</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.84521</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7975</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.75915</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49191</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.02257</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.02509</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.02159</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.75118</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.22698</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.65239</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46331</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61334</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.49692</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.54288</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.14385</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.14801</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50154</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46344</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47736</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50383</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3171</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25258</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.06984</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.12207</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.06004</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.06376</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.04839</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.17957</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.20779</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.18572</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.19203</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.23624</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.20693</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.21805</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.00679</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.07873999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.23052</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.22924</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.21694</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.18204</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.21725</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.12335</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>8.999999999999999e-05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19385</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04059</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.13554</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01635</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.26044</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.25844</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.21891</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31995</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.23299</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91411</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630399999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29608</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8696499999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6138899999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33076</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03283</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53073</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39998</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20709</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53839</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.25483</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.22195</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.25646</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.09147</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>-0.00936</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.2297</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8802000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.7867999999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>-0.04011</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.21153</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.19695</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.23845</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.12195</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.14109</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.07954</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.14876</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.22195</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.21998</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.16831</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-0.01475</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-0.02144</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>-0.02739</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.23596</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.79671</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.15187</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.06232</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.02741</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.11063</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.02891</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.16501</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.18287</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.20346</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.14138</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.21673</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.02298</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.03335</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.16081</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.14041</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.12605</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.08161</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.13175</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.14761</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.18579</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.18982</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.18289</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.08175</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.13539</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.24867</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.21766</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.27053</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.19258</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.22276</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.17976</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.15989</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.18277</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.20965</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.21092</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.15988</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.11316</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.20508</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.24095</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.21797</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.16775</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.08424</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.03298</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.64667</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.31902</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.03765</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.5799500000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.67006</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.08867</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.03675</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>-0.03115</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.17635</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.008539999999999999</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.21851</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.18531</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24879</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.22699</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.04181</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.19591</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.22807</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.23361</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.23066</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.19291</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.23369</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.17356</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.11534</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.24195</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.23171</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.08852</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.20833</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.04629999999999999</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.14432</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.22513</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.11708</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.10897</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.11317</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.13223</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.17379</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.05927</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.17623</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.04667</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.00451</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.03103</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.21795</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.03089</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.02758</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.20195</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.19795</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.20705</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.19295</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.01992</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.20204</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.18006</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.20289</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.04012</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02344</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.21912</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01227</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.03325</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.03674</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03711</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.19024</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.08752</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.17804</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.10134</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.14198</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.16946</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.03263</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.09290000000000001</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.03154</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.02823</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.06551</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>-0.03871</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.08403000000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.14493</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.01395</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.08823</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.06548000000000001</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.07398</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.25172</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.09762</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.14259</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.10872</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.05489</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.13592</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.14948</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.15888</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.14992</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.15888</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.15368</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.07551000000000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.06589</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.12244</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.14492</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.19512</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.18078</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.21354</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.25864</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.21757</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27429</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.24301</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.19723</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.22419</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.23675</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.17014</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.19003</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.13192</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.14165</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.16691</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.18897</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.13279</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.14553</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.23856</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.18365</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.21671</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.09139</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.21997</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.21382</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.16279</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.16123</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.09926</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.20553</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.09908</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.09042</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.14251</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.13739</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.10804</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.15879</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.09476000000000001</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.09390000000000001</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.14437</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.13363</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.15478</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.15124</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.22928</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.15457</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.15717</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.22359</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.22204</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.2166</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.15805</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.15746</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.13592</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.02084</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.09826</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.22081</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.16157</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.03603</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.56792</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.14842</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.26618</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.23847</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.23528</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.09999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.18367</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.24482</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.21311</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.21935</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.58399</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.18639</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.20539</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.17952</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.08756</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.04981</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.09115000000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.07635</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.01058</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.09554</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.08120999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.10807</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.10602</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.11684</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-0.01789</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20501</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.07234</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>-0.04269</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.13519</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.21701</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.05444</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.22807</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.17158</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.14258</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.14777</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.14897</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.21955</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.15822</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.16302</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.15842</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.21808</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.17355</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.20457</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.20667</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.15518</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.14984</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.10401</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.12556</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.22204</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.18642</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>-0.01018</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.10319</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.15581</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.17099</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.23637</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.20497</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.14846</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.12383</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.22712</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.02971</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>-0.03691</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.23506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-0.02696</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.23012</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.23114</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.23014</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.07490000000000001</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.22769</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.11082</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.09379000000000001</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.08320999999999999</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.02516</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.20446</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.11711</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.22013</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.13137</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.07334</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.22512</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.12911</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.11082</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.21681</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.10082</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.11124</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.09065999999999999</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.14936</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.10038</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.17908</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.21265</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.24861</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.24861</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.25001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.19032</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.20789</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.21431</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.23198</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.18699</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.23391</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.18605</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.23011</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.15611</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.08406999999999999</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.13748</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.14343</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.52003</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>-0.00567</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>-0.01806</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.23377</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.15371</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.17866</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.23943</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.23909</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.23912</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.17984</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.23306</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.24021</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.23666</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.23965</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.22777</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.09879</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.24607</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.23198</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.23878</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.20886</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.10174</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25005</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03345</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.00158</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20362</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15057</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21353</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.19999</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.20042</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.20883</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20299</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20476</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.20466</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.12996</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.23632</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.25474</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.54928</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5125700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5331900000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.72177</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>-0.01843</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.14802</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.25694</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.16722</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.17871</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.07798999999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.06631999999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.03437</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.09237999999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.10989</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.01113</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.00712</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.06922</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.00915</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-0.01567</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.02307</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.21123</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6845599999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.03092</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04387</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.16808</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.22535</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.22588</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>-0.01575</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.66308</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.50713</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-0.03343</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-0.03839</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.06772</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.08029</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.12645</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.10471</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.07023</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.23732</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.10748</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.19334</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.01596</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.23376</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.17576</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.09965</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.19378</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.11185</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.13301</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.08935999999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.26059</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.03947999999999999</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.12733</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.02832</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.19452</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.22524</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02269</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25186</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.23572</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.15178</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.16411</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.12869</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.09555</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.006730000000000001</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>-0.00658</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.07446999999999999</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.03414</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.02026</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>-0.00783</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>-0.01657</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.06923</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.00046</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.10175</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.09364</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.10091</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.07818000000000001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.12055</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15759</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14866</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02671</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03879</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03879</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.18748</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.20168</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.16773</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22752</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.17687</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.16885</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.14702</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.10707</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.23251</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22986</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.16241</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.13899</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.13648</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.19601</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.11403</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.18403</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.16708</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.15447</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.12607</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18102</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.21817</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.02682</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.03791</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.02698</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.23237</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.03189</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.23718</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.76902</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8668400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03361</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16668</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>5.999999999999999e-05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04024</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.14012</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.11484</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.20327</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.17446</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.11497</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.82394</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7281299999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7281299999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.72811</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.82494</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.21535</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.18734</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.10402</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.10402</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-0.01347</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.19451</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.08773</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.07869</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.23099</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.13169</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.11556</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.26626</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.22322</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.24525</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.18622</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.20449</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.16412</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.07187</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.13571</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.08735</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.10041</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.06462000000000001</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.08477</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.06539</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.05815</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.10358</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.10714</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.12169</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.13566</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.13512</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.16104</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.14724</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.13447</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.14581</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.15118</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.15118</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.14053</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.13506</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.13932</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.13505</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.16646</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.08893999999999999</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.11203</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.13506</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.19825</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24317</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.23752</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25832</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.22498</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.6990700000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.13693</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.80187</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.09736</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.24499</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>-0.04022</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.10588</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.19333</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.11347</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.15496</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.15721</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.15629</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.23016</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.15363</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.14192</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.08990999999999999</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.12454</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.17725</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.12404</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.14197</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.14066</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.13328</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.16728</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.18262</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.17679</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.17713</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.15009</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.22051</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.14339</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.12717</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.10083</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.25317</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.17737</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.23677</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.17619</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.25412</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.23675</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.2441</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.23999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.21125</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.22202</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.20369</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.19577</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.23514</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.25897</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.23777</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.22718</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.23501</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.19482</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.20094</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.20623</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>-0.03414</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8154600000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72199</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.14475</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.13675</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.18571</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.16773</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.15678</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.13006</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.08131000000000001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.08827</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.14167</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.23407</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.13592</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.11973</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.13571</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.11514</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.10461</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.23758</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.03274000000000001</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.26701</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.24563</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.13309</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.13533</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.23712</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.24828</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12414</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.20938</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.14193</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.2223</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09406999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.17106</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.05265</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14642</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18133</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.20238</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.12246</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.18166</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.24608</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.18992</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.19075</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.18506</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.19949</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.18281</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.21887</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.21558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.007719999999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.21811</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.24432</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.21899</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.20701</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.21176</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.25327</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.23909</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.25638</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.16707</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.44246</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.25063</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.18986</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.26774</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.27552</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.25221</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.12121</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.26132</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.20483</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.26949</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.23632</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.24657</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.25274</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.25253</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14704</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24021</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13672</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.04316</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17838</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23104</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26965</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15755</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22898</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20206</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14822</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.21085</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1.3785</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>1.29755</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>1.34449</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1.29956</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.30797</v>
       </c>
     </row>
   </sheetData>
